--- a/database/event/2471/event_2471_evp_summary.xlsx
+++ b/database/event/2471/event_2471_evp_summary.xlsx
@@ -492,127 +492,127 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.6301</v>
+        <v>8.0968</v>
       </c>
       <c r="C2" t="n">
-        <v>4.3806</v>
+        <v>5.3497</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2571</v>
+        <v>2.7819</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6301</v>
+        <v>8.0968</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4329</v>
+        <v>4.6284</v>
       </c>
       <c r="G2" t="n">
-        <v>4.1972</v>
+        <v>3.4684</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4329</v>
+        <v>4.9543</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4329</v>
+        <v>4.9543</v>
       </c>
       <c r="J2" t="n">
-        <v>4.1972</v>
+        <v>3.4684</v>
       </c>
       <c r="K2" t="n">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="L2" t="n">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="M2" t="n">
-        <v>6.6301</v>
+        <v>8.422699999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>316</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.5925</v>
+        <v>7.8163</v>
       </c>
       <c r="C3" t="n">
-        <v>4.3558</v>
+        <v>5.1644</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2419</v>
+        <v>2.6701</v>
       </c>
       <c r="E3" t="n">
-        <v>6.5925</v>
+        <v>7.8163</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9107</v>
+        <v>3.6191</v>
       </c>
       <c r="G3" t="n">
-        <v>5.6818</v>
+        <v>4.1972</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9107</v>
+        <v>3.6191</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9107</v>
+        <v>3.6191</v>
       </c>
       <c r="J3" t="n">
-        <v>5.6818</v>
+        <v>4.1972</v>
       </c>
       <c r="K3" t="n">
-        <v>126</v>
+        <v>85</v>
       </c>
       <c r="L3" t="n">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="M3" t="n">
-        <v>6.5925</v>
+        <v>7.8163</v>
       </c>
       <c r="N3" t="n">
-        <v>349</v>
+        <v>316</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.5829</v>
+        <v>7.4383</v>
       </c>
       <c r="C4" t="n">
-        <v>4.3495</v>
+        <v>4.9146</v>
       </c>
       <c r="D4" t="n">
-        <v>2.238</v>
+        <v>2.5195</v>
       </c>
       <c r="E4" t="n">
-        <v>6.5829</v>
+        <v>7.4383</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1145</v>
+        <v>1.7565</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4684</v>
+        <v>5.6818</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1145</v>
+        <v>1.7565</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1145</v>
+        <v>1.7565</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4684</v>
+        <v>5.6818</v>
       </c>
       <c r="K4" t="n">
         <v>126</v>
@@ -621,7 +621,7 @@
         <v>223</v>
       </c>
       <c r="M4" t="n">
-        <v>6.5829</v>
+        <v>7.4383</v>
       </c>
       <c r="N4" t="n">
         <v>349</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.5084</v>
+        <v>5.8713</v>
       </c>
       <c r="C5" t="n">
-        <v>2.9788</v>
+        <v>3.8793</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3999</v>
+        <v>1.8952</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5084</v>
+        <v>5.8713</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7242</v>
+        <v>4.0871</v>
       </c>
       <c r="G5" t="n">
         <v>1.7842</v>
       </c>
       <c r="H5" t="n">
-        <v>2.7242</v>
+        <v>4.1055</v>
       </c>
       <c r="I5" t="n">
-        <v>2.7242</v>
+        <v>4.1055</v>
       </c>
       <c r="J5" t="n">
         <v>1.7842</v>
@@ -667,7 +667,7 @@
         <v>129</v>
       </c>
       <c r="M5" t="n">
-        <v>4.5084</v>
+        <v>5.8897</v>
       </c>
       <c r="N5" t="n">
         <v>243</v>
@@ -676,369 +676,369 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.6341</v>
+        <v>4.996</v>
       </c>
       <c r="C6" t="n">
-        <v>2.4011</v>
+        <v>3.301</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0467</v>
+        <v>1.5465</v>
       </c>
       <c r="E6" t="n">
-        <v>3.6341</v>
+        <v>4.996</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2786</v>
+        <v>4.4555</v>
       </c>
       <c r="G6" t="n">
-        <v>2.3555</v>
+        <v>0.5405</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2786</v>
+        <v>4.6832</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2786</v>
+        <v>4.6832</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3555</v>
+        <v>0.5405</v>
       </c>
       <c r="K6" t="n">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="L6" t="n">
-        <v>129</v>
+        <v>65</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6341</v>
+        <v>5.2237</v>
       </c>
       <c r="N6" t="n">
-        <v>243</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.5131</v>
+        <v>4.4914</v>
       </c>
       <c r="C7" t="n">
-        <v>2.3212</v>
+        <v>2.9676</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9979</v>
+        <v>1.3455</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5131</v>
+        <v>4.4914</v>
       </c>
       <c r="F7" t="n">
-        <v>1.12</v>
+        <v>4.4972</v>
       </c>
       <c r="G7" t="n">
-        <v>2.3931</v>
+        <v>-0.0058</v>
       </c>
       <c r="H7" t="n">
-        <v>1.12</v>
+        <v>4.7486</v>
       </c>
       <c r="I7" t="n">
-        <v>1.12</v>
+        <v>4.7486</v>
       </c>
       <c r="J7" t="n">
-        <v>2.3931</v>
+        <v>-0.0058</v>
       </c>
       <c r="K7" t="n">
-        <v>126</v>
+        <v>60</v>
       </c>
       <c r="L7" t="n">
-        <v>223</v>
+        <v>79</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5131</v>
+        <v>4.7428</v>
       </c>
       <c r="N7" t="n">
-        <v>349</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.452</v>
+        <v>4.4533</v>
       </c>
       <c r="C8" t="n">
-        <v>2.2808</v>
+        <v>2.9424</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9732</v>
+        <v>1.3303</v>
       </c>
       <c r="E8" t="n">
-        <v>3.452</v>
+        <v>4.4533</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9115</v>
+        <v>2.0978</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5405</v>
+        <v>2.3555</v>
       </c>
       <c r="H8" t="n">
-        <v>2.9115</v>
+        <v>2.0978</v>
       </c>
       <c r="I8" t="n">
-        <v>2.9115</v>
+        <v>2.0978</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5405</v>
+        <v>2.3555</v>
       </c>
       <c r="K8" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="L8" t="n">
-        <v>65</v>
+        <v>129</v>
       </c>
       <c r="M8" t="n">
-        <v>3.452</v>
+        <v>4.4533</v>
       </c>
       <c r="N8" t="n">
-        <v>170</v>
+        <v>243</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.314</v>
+        <v>4.3525</v>
       </c>
       <c r="C9" t="n">
-        <v>2.1896</v>
+        <v>2.8758</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9174</v>
+        <v>1.2901</v>
       </c>
       <c r="E9" t="n">
-        <v>3.314</v>
+        <v>4.3525</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1372</v>
+        <v>1.9594</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1768</v>
+        <v>2.3931</v>
       </c>
       <c r="H9" t="n">
-        <v>2.1372</v>
+        <v>1.9594</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1372</v>
+        <v>1.9594</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1768</v>
+        <v>2.3931</v>
       </c>
       <c r="K9" t="n">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="L9" t="n">
-        <v>77</v>
+        <v>223</v>
       </c>
       <c r="M9" t="n">
-        <v>3.314</v>
+        <v>4.3525</v>
       </c>
       <c r="N9" t="n">
-        <v>225</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.5379</v>
+        <v>4.2038</v>
       </c>
       <c r="C10" t="n">
-        <v>1.6768</v>
+        <v>2.7775</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6039</v>
+        <v>1.2309</v>
       </c>
       <c r="E10" t="n">
-        <v>2.5379</v>
+        <v>4.2038</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5437</v>
+        <v>3.027</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0058</v>
+        <v>1.1768</v>
       </c>
       <c r="H10" t="n">
-        <v>2.5437</v>
+        <v>3.027</v>
       </c>
       <c r="I10" t="n">
-        <v>2.5437</v>
+        <v>3.027</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0058</v>
+        <v>1.1768</v>
       </c>
       <c r="K10" t="n">
-        <v>60</v>
+        <v>148</v>
       </c>
       <c r="L10" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="M10" t="n">
-        <v>2.5379</v>
+        <v>4.2038</v>
       </c>
       <c r="N10" t="n">
-        <v>139</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>fox</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.3949</v>
+        <v>3.0673</v>
       </c>
       <c r="C11" t="n">
-        <v>1.5824</v>
+        <v>2.0266</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5461</v>
+        <v>0.7781</v>
       </c>
       <c r="E11" t="n">
-        <v>2.3949</v>
+        <v>3.0673</v>
       </c>
       <c r="F11" t="n">
-        <v>0.554</v>
+        <v>3.0673</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8409</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.554</v>
+        <v>3.0673</v>
       </c>
       <c r="I11" t="n">
-        <v>0.554</v>
+        <v>3.0673</v>
       </c>
       <c r="J11" t="n">
-        <v>1.8409</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>114</v>
+        <v>155</v>
       </c>
       <c r="L11" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.3949</v>
+        <v>3.0673</v>
       </c>
       <c r="N11" t="n">
-        <v>243</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.3313</v>
+        <v>2.8799</v>
       </c>
       <c r="C12" t="n">
-        <v>1.5403</v>
+        <v>1.9028</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5204</v>
+        <v>0.7034</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3313</v>
+        <v>2.8799</v>
       </c>
       <c r="F12" t="n">
-        <v>1.52</v>
+        <v>2.8799</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8113</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.52</v>
+        <v>2.8799</v>
       </c>
       <c r="I12" t="n">
-        <v>1.52</v>
+        <v>2.8799</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8113</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="L12" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.3313</v>
+        <v>2.8799</v>
       </c>
       <c r="N12" t="n">
-        <v>230</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.2853</v>
+        <v>2.7061</v>
       </c>
       <c r="C13" t="n">
-        <v>1.5099</v>
+        <v>1.788</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5018</v>
+        <v>0.6342</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2853</v>
+        <v>2.7061</v>
       </c>
       <c r="F13" t="n">
-        <v>0.237</v>
+        <v>2.7061</v>
       </c>
       <c r="G13" t="n">
-        <v>2.0483</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.237</v>
+        <v>2.7061</v>
       </c>
       <c r="I13" t="n">
-        <v>0.237</v>
+        <v>2.7061</v>
       </c>
       <c r="J13" t="n">
-        <v>2.0483</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="L13" t="n">
-        <v>231</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.2853</v>
+        <v>2.7061</v>
       </c>
       <c r="N13" t="n">
-        <v>316</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1618</v>
+        <v>2.6769</v>
       </c>
       <c r="C14" t="n">
-        <v>1.4283</v>
+        <v>1.7687</v>
       </c>
       <c r="D14" t="n">
-        <v>0.452</v>
+        <v>0.6226</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1618</v>
+        <v>2.6769</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0844</v>
+        <v>2.5995</v>
       </c>
       <c r="G14" t="n">
         <v>0.0774</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0844</v>
+        <v>2.5995</v>
       </c>
       <c r="I14" t="n">
-        <v>2.0844</v>
+        <v>2.5995</v>
       </c>
       <c r="J14" t="n">
         <v>0.0774</v>
@@ -1081,7 +1081,7 @@
         <v>79</v>
       </c>
       <c r="M14" t="n">
-        <v>2.1618</v>
+        <v>2.6769</v>
       </c>
       <c r="N14" t="n">
         <v>139</v>
@@ -1090,679 +1090,679 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>fox</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.9356</v>
+        <v>2.4474</v>
       </c>
       <c r="C15" t="n">
-        <v>1.2789</v>
+        <v>1.617</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3606</v>
+        <v>0.5311</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9356</v>
+        <v>2.4474</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9356</v>
+        <v>0.6065</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1.8409</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9356</v>
+        <v>0.6065</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9356</v>
+        <v>0.6065</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1.8409</v>
       </c>
       <c r="K15" t="n">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="M15" t="n">
-        <v>1.9356</v>
+        <v>2.4474</v>
       </c>
       <c r="N15" t="n">
-        <v>141</v>
+        <v>243</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8717</v>
+        <v>2.3313</v>
       </c>
       <c r="C16" t="n">
-        <v>1.2367</v>
+        <v>1.5403</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3348</v>
+        <v>0.4849</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8717</v>
+        <v>2.3313</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.409</v>
+        <v>1.52</v>
       </c>
       <c r="G16" t="n">
-        <v>2.2807</v>
+        <v>0.8113</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.409</v>
+        <v>1.52</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.409</v>
+        <v>1.52</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2807</v>
+        <v>0.8113</v>
       </c>
       <c r="K16" t="n">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="L16" t="n">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="M16" t="n">
-        <v>1.8717</v>
+        <v>2.3313</v>
       </c>
       <c r="N16" t="n">
-        <v>243</v>
+        <v>230</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.7958</v>
+        <v>2.328</v>
       </c>
       <c r="C17" t="n">
-        <v>1.1865</v>
+        <v>1.5382</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3041</v>
+        <v>0.4836</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7958</v>
+        <v>2.328</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8539</v>
+        <v>0.2797</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0581</v>
+        <v>2.0483</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8539</v>
+        <v>0.2797</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8539</v>
+        <v>0.2797</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0581</v>
+        <v>2.0483</v>
       </c>
       <c r="K17" t="n">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="L17" t="n">
-        <v>121</v>
+        <v>231</v>
       </c>
       <c r="M17" t="n">
-        <v>1.7958</v>
+        <v>2.328</v>
       </c>
       <c r="N17" t="n">
-        <v>230</v>
+        <v>316</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.6974</v>
+        <v>2.1513</v>
       </c>
       <c r="C18" t="n">
-        <v>1.1215</v>
+        <v>1.4214</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2643</v>
+        <v>0.4132</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6974</v>
+        <v>2.1513</v>
       </c>
       <c r="F18" t="n">
-        <v>1.616</v>
+        <v>2.149</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0814</v>
+        <v>0.0023</v>
       </c>
       <c r="H18" t="n">
-        <v>1.616</v>
+        <v>2.149</v>
       </c>
       <c r="I18" t="n">
-        <v>1.616</v>
+        <v>2.149</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0814</v>
+        <v>0.0023</v>
       </c>
       <c r="K18" t="n">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="L18" t="n">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6974</v>
+        <v>2.1513</v>
       </c>
       <c r="N18" t="n">
-        <v>316</v>
+        <v>349</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.5782</v>
+        <v>2.1501</v>
       </c>
       <c r="C19" t="n">
-        <v>1.0428</v>
+        <v>1.4206</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2162</v>
+        <v>0.4127</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5782</v>
+        <v>2.1501</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5782</v>
+        <v>2.1501</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5782</v>
+        <v>2.1501</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5782</v>
+        <v>2.1501</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.5782</v>
+        <v>2.1501</v>
       </c>
       <c r="N19" t="n">
-        <v>102</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4946</v>
+        <v>2.1076</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9875</v>
+        <v>1.3925</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1824</v>
+        <v>0.3958</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4946</v>
+        <v>2.1076</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2029</v>
+        <v>2.0262</v>
       </c>
       <c r="G20" t="n">
-        <v>2.6975</v>
+        <v>0.0814</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2029</v>
+        <v>2.0262</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2029</v>
+        <v>2.0262</v>
       </c>
       <c r="J20" t="n">
-        <v>2.6975</v>
+        <v>0.0814</v>
       </c>
       <c r="K20" t="n">
-        <v>126</v>
+        <v>85</v>
       </c>
       <c r="L20" t="n">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4946</v>
+        <v>2.1076</v>
       </c>
       <c r="N20" t="n">
-        <v>349</v>
+        <v>316</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>twist</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.4798</v>
+        <v>2.0707</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9777</v>
+        <v>1.3682</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1764</v>
+        <v>0.3811</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4798</v>
+        <v>2.0707</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0062</v>
+        <v>2.9375</v>
       </c>
       <c r="G21" t="n">
-        <v>1.4859</v>
+        <v>-0.8668</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0062</v>
+        <v>2.9375</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0062</v>
+        <v>2.9375</v>
       </c>
       <c r="J21" t="n">
-        <v>1.4859</v>
+        <v>-0.8668</v>
       </c>
       <c r="K21" t="n">
-        <v>109</v>
+        <v>60</v>
       </c>
       <c r="L21" t="n">
-        <v>121</v>
+        <v>79</v>
       </c>
       <c r="M21" t="n">
-        <v>1.4797</v>
+        <v>2.0707</v>
       </c>
       <c r="N21" t="n">
-        <v>230</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.412</v>
+        <v>2.0587</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9329</v>
+        <v>1.3602</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1491</v>
+        <v>0.3763</v>
       </c>
       <c r="E22" t="n">
-        <v>1.412</v>
+        <v>2.0587</v>
       </c>
       <c r="F22" t="n">
-        <v>1.412</v>
+        <v>2.1168</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.0581</v>
       </c>
       <c r="H22" t="n">
-        <v>1.412</v>
+        <v>2.1168</v>
       </c>
       <c r="I22" t="n">
-        <v>1.412</v>
+        <v>2.1168</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.0581</v>
       </c>
       <c r="K22" t="n">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="M22" t="n">
-        <v>1.412</v>
+        <v>2.0587</v>
       </c>
       <c r="N22" t="n">
-        <v>126</v>
+        <v>230</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.3928</v>
+        <v>2.0394</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9203</v>
+        <v>1.3475</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1413</v>
+        <v>0.3686</v>
       </c>
       <c r="E23" t="n">
-        <v>1.3928</v>
+        <v>2.0394</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3928</v>
+        <v>2.7574</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.718</v>
       </c>
       <c r="H23" t="n">
-        <v>1.3928</v>
+        <v>2.7574</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3928</v>
+        <v>2.7574</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.718</v>
       </c>
       <c r="K23" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M23" t="n">
-        <v>1.3928</v>
+        <v>2.0394</v>
       </c>
       <c r="N23" t="n">
-        <v>155</v>
+        <v>221</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>twist</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.3814</v>
+        <v>1.9988</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9127</v>
+        <v>1.3206</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1367</v>
+        <v>0.3524</v>
       </c>
       <c r="E24" t="n">
-        <v>1.3814</v>
+        <v>1.9988</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3814</v>
+        <v>0.5129</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1.4859</v>
       </c>
       <c r="H24" t="n">
-        <v>1.3814</v>
+        <v>0.5129</v>
       </c>
       <c r="I24" t="n">
-        <v>1.3814</v>
+        <v>0.5129</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1.4859</v>
       </c>
       <c r="K24" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="M24" t="n">
-        <v>1.3814</v>
+        <v>1.9988</v>
       </c>
       <c r="N24" t="n">
-        <v>110</v>
+        <v>230</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.3423</v>
+        <v>1.8717</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8869</v>
+        <v>1.2367</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1209</v>
+        <v>0.3018</v>
       </c>
       <c r="E25" t="n">
-        <v>1.3423</v>
+        <v>1.8717</v>
       </c>
       <c r="F25" t="n">
-        <v>2.2091</v>
+        <v>-0.409</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.8668</v>
+        <v>2.2807</v>
       </c>
       <c r="H25" t="n">
-        <v>2.2091</v>
+        <v>-0.409</v>
       </c>
       <c r="I25" t="n">
-        <v>2.2091</v>
+        <v>-0.409</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.8668</v>
+        <v>2.2807</v>
       </c>
       <c r="K25" t="n">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="L25" t="n">
-        <v>79</v>
+        <v>129</v>
       </c>
       <c r="M25" t="n">
-        <v>1.3423</v>
+        <v>1.8717</v>
       </c>
       <c r="N25" t="n">
-        <v>139</v>
+        <v>243</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.3087</v>
+        <v>1.7147</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8647</v>
+        <v>1.1329</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1073</v>
+        <v>0.2392</v>
       </c>
       <c r="E26" t="n">
-        <v>1.3087</v>
+        <v>1.7147</v>
       </c>
       <c r="F26" t="n">
-        <v>1.3087</v>
+        <v>1.7147</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.3087</v>
+        <v>1.7147</v>
       </c>
       <c r="I26" t="n">
-        <v>1.3087</v>
+        <v>1.7147</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.3087</v>
+        <v>1.7147</v>
       </c>
       <c r="N26" t="n">
-        <v>126</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.2795</v>
+        <v>1.562</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8454</v>
+        <v>1.032</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0955</v>
+        <v>0.1784</v>
       </c>
       <c r="E27" t="n">
-        <v>1.2795</v>
+        <v>1.562</v>
       </c>
       <c r="F27" t="n">
-        <v>1.9975</v>
+        <v>-1.1355</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.718</v>
+        <v>2.6975</v>
       </c>
       <c r="H27" t="n">
-        <v>1.9975</v>
+        <v>-1.1355</v>
       </c>
       <c r="I27" t="n">
-        <v>1.9975</v>
+        <v>-1.1355</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.718</v>
+        <v>2.6975</v>
       </c>
       <c r="K27" t="n">
-        <v>158</v>
+        <v>126</v>
       </c>
       <c r="L27" t="n">
-        <v>63</v>
+        <v>223</v>
       </c>
       <c r="M27" t="n">
-        <v>1.2795</v>
+        <v>1.562</v>
       </c>
       <c r="N27" t="n">
-        <v>221</v>
+        <v>349</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.234</v>
+        <v>1.4963</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8153</v>
+        <v>0.9886</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0771</v>
+        <v>0.1522</v>
       </c>
       <c r="E28" t="n">
-        <v>1.234</v>
+        <v>1.4963</v>
       </c>
       <c r="F28" t="n">
-        <v>1.2317</v>
+        <v>1.4963</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0023</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.2317</v>
+        <v>1.4963</v>
       </c>
       <c r="I28" t="n">
-        <v>1.2317</v>
+        <v>1.4963</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0023</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
         <v>126</v>
       </c>
       <c r="L28" t="n">
-        <v>223</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.234</v>
+        <v>1.4963</v>
       </c>
       <c r="N28" t="n">
-        <v>349</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.179</v>
+        <v>1.4924</v>
       </c>
       <c r="C29" t="n">
-        <v>0.779</v>
+        <v>0.9861</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0549</v>
+        <v>0.1507</v>
       </c>
       <c r="E29" t="n">
-        <v>1.179</v>
+        <v>1.4924</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9608</v>
+        <v>2.4924</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2182</v>
+        <v>-1</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9608</v>
+        <v>2.4924</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9608</v>
+        <v>2.4924</v>
       </c>
       <c r="J29" t="n">
-        <v>0.2182</v>
+        <v>-1</v>
       </c>
       <c r="K29" t="n">
         <v>158</v>
@@ -1771,7 +1771,7 @@
         <v>63</v>
       </c>
       <c r="M29" t="n">
-        <v>1.179</v>
+        <v>1.4924</v>
       </c>
       <c r="N29" t="n">
         <v>221</v>
@@ -1780,47 +1780,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.1699</v>
+        <v>1.3814</v>
       </c>
       <c r="C30" t="n">
-        <v>0.773</v>
+        <v>0.9127</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0513</v>
+        <v>0.1064</v>
       </c>
       <c r="E30" t="n">
-        <v>1.1699</v>
+        <v>1.3814</v>
       </c>
       <c r="F30" t="n">
-        <v>1.1699</v>
+        <v>1.3814</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.1699</v>
+        <v>1.3814</v>
       </c>
       <c r="I30" t="n">
-        <v>1.1699</v>
+        <v>1.3814</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.1699</v>
+        <v>1.3814</v>
       </c>
       <c r="N30" t="n">
-        <v>141</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.1614</v>
+        <v>1.3446</v>
       </c>
       <c r="C31" t="n">
-        <v>0.7674</v>
+        <v>0.8884</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0478</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>1.1614</v>
+        <v>1.3446</v>
       </c>
       <c r="F31" t="n">
-        <v>1.1614</v>
+        <v>1.3446</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.1614</v>
+        <v>1.3446</v>
       </c>
       <c r="I31" t="n">
-        <v>1.1614</v>
+        <v>1.3446</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.1614</v>
+        <v>1.3446</v>
       </c>
       <c r="N31" t="n">
         <v>141</v>
@@ -1872,185 +1872,185 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.0671</v>
+        <v>1.3087</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7050999999999999</v>
+        <v>0.8647</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0097</v>
+        <v>0.0775</v>
       </c>
       <c r="E32" t="n">
-        <v>1.0671</v>
+        <v>1.3087</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3342</v>
+        <v>1.3087</v>
       </c>
       <c r="G32" t="n">
-        <v>0.7329</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.3342</v>
+        <v>1.3087</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3342</v>
+        <v>1.3087</v>
       </c>
       <c r="J32" t="n">
-        <v>0.7329</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="L32" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.0671</v>
+        <v>1.3087</v>
       </c>
       <c r="N32" t="n">
-        <v>170</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.9602000000000001</v>
+        <v>1.2874</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6344</v>
+        <v>0.8506</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0335</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9602000000000001</v>
+        <v>1.2874</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9602000000000001</v>
+        <v>1.2874</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9602000000000001</v>
+        <v>1.2874</v>
       </c>
       <c r="I33" t="n">
-        <v>0.9602000000000001</v>
+        <v>1.2874</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.9602000000000001</v>
+        <v>1.2874</v>
       </c>
       <c r="N33" t="n">
-        <v>126</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8999</v>
+        <v>1.179</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5946</v>
+        <v>0.779</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0578</v>
+        <v>0.0258</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8999</v>
+        <v>1.179</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8999</v>
+        <v>0.9608</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>0.2182</v>
       </c>
       <c r="H34" t="n">
-        <v>0.8999</v>
+        <v>0.9608</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8999</v>
+        <v>0.9608</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>0.2182</v>
       </c>
       <c r="K34" t="n">
-        <v>84</v>
+        <v>158</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M34" t="n">
-        <v>0.8999</v>
+        <v>1.179</v>
       </c>
       <c r="N34" t="n">
-        <v>84</v>
+        <v>221</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7826</v>
+        <v>1.0671</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5171</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1052</v>
+        <v>-0.0188</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7826</v>
+        <v>1.0671</v>
       </c>
       <c r="F35" t="n">
-        <v>1.7826</v>
+        <v>0.3342</v>
       </c>
       <c r="G35" t="n">
-        <v>-1</v>
+        <v>0.7329</v>
       </c>
       <c r="H35" t="n">
-        <v>1.7826</v>
+        <v>0.3342</v>
       </c>
       <c r="I35" t="n">
-        <v>1.7826</v>
+        <v>0.3342</v>
       </c>
       <c r="J35" t="n">
-        <v>-1</v>
+        <v>0.7329</v>
       </c>
       <c r="K35" t="n">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="L35" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7826</v>
+        <v>1.0671</v>
       </c>
       <c r="N35" t="n">
-        <v>221</v>
+        <v>170</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7611</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="C36" t="n">
-        <v>0.5029</v>
+        <v>0.6511</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1139</v>
+        <v>-0.0513</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7611</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>0.7613</v>
+        <v>0.9856</v>
       </c>
       <c r="G36" t="n">
         <v>-0.0002</v>
       </c>
       <c r="H36" t="n">
-        <v>0.7613</v>
+        <v>0.9856</v>
       </c>
       <c r="I36" t="n">
-        <v>0.7613</v>
+        <v>0.9856</v>
       </c>
       <c r="J36" t="n">
         <v>-0.0002</v>
@@ -2093,7 +2093,7 @@
         <v>79</v>
       </c>
       <c r="M36" t="n">
-        <v>0.7611</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="N36" t="n">
         <v>139</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.745</v>
+        <v>0.9555</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4922</v>
+        <v>0.6313</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1204</v>
+        <v>-0.06320000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>0.745</v>
+        <v>0.9555</v>
       </c>
       <c r="F37" t="n">
-        <v>0.745</v>
+        <v>0.9555</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.745</v>
+        <v>0.9555</v>
       </c>
       <c r="I37" t="n">
-        <v>0.745</v>
+        <v>0.9555</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.745</v>
+        <v>0.9555</v>
       </c>
       <c r="N37" t="n">
         <v>155</v>
@@ -2148,32 +2148,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.664</v>
+        <v>0.9443</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4387</v>
+        <v>0.6239</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1531</v>
+        <v>-0.0677</v>
       </c>
       <c r="E38" t="n">
-        <v>0.664</v>
+        <v>0.9443</v>
       </c>
       <c r="F38" t="n">
-        <v>0.664</v>
+        <v>0.9443</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.664</v>
+        <v>0.9443</v>
       </c>
       <c r="I38" t="n">
-        <v>0.664</v>
+        <v>0.9443</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.664</v>
+        <v>0.9443</v>
       </c>
       <c r="N38" t="n">
         <v>89</v>
@@ -2194,127 +2194,127 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6061</v>
+        <v>0.8999</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4005</v>
+        <v>0.5946</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1765</v>
+        <v>-0.0854</v>
       </c>
       <c r="E39" t="n">
-        <v>0.6061</v>
+        <v>0.8999</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4889</v>
+        <v>0.8999</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1172</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.4889</v>
+        <v>0.8999</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4889</v>
+        <v>0.8999</v>
       </c>
       <c r="J39" t="n">
-        <v>0.1172</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="L39" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.6061</v>
+        <v>0.8999</v>
       </c>
       <c r="N39" t="n">
-        <v>139</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5825</v>
+        <v>0.8439</v>
       </c>
       <c r="C40" t="n">
-        <v>0.3849</v>
+        <v>0.5576</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.186</v>
+        <v>-0.1077</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5825</v>
+        <v>0.8439</v>
       </c>
       <c r="F40" t="n">
-        <v>0.5825</v>
+        <v>0.8439</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5825</v>
+        <v>0.8439</v>
       </c>
       <c r="I40" t="n">
-        <v>0.5825</v>
+        <v>0.8439</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.5825</v>
+        <v>0.8439</v>
       </c>
       <c r="N40" t="n">
-        <v>102</v>
+        <v>89</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>RUBINO</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5396</v>
+        <v>0.7039</v>
       </c>
       <c r="C41" t="n">
-        <v>0.3565</v>
+        <v>0.4651</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2034</v>
+        <v>-0.1635</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5396</v>
+        <v>0.7039</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3481</v>
+        <v>1.4274</v>
       </c>
       <c r="G41" t="n">
-        <v>0.1915</v>
+        <v>-0.7235</v>
       </c>
       <c r="H41" t="n">
-        <v>0.3481</v>
+        <v>1.4274</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3481</v>
+        <v>1.4274</v>
       </c>
       <c r="J41" t="n">
-        <v>0.1915</v>
+        <v>-0.7235</v>
       </c>
       <c r="K41" t="n">
         <v>148</v>
@@ -2323,7 +2323,7 @@
         <v>77</v>
       </c>
       <c r="M41" t="n">
-        <v>0.5396000000000001</v>
+        <v>0.7039</v>
       </c>
       <c r="N41" t="n">
         <v>225</v>
@@ -2332,47 +2332,47 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5144</v>
+        <v>0.6988</v>
       </c>
       <c r="C42" t="n">
-        <v>0.3399</v>
+        <v>0.4617</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2136</v>
+        <v>-0.1655</v>
       </c>
       <c r="E42" t="n">
-        <v>0.5144</v>
+        <v>0.6988</v>
       </c>
       <c r="F42" t="n">
-        <v>0.5144</v>
+        <v>0.5816</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>0.1172</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5144</v>
+        <v>0.5816</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5144</v>
+        <v>0.5816</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.1172</v>
       </c>
       <c r="K42" t="n">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M42" t="n">
-        <v>0.5144</v>
+        <v>0.6988</v>
       </c>
       <c r="N42" t="n">
-        <v>89</v>
+        <v>139</v>
       </c>
     </row>
     <row r="43">
@@ -2382,28 +2382,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.438</v>
+        <v>0.6856</v>
       </c>
       <c r="C43" t="n">
-        <v>0.2894</v>
+        <v>0.453</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2444</v>
+        <v>-0.1708</v>
       </c>
       <c r="E43" t="n">
-        <v>0.438</v>
+        <v>0.6856</v>
       </c>
       <c r="F43" t="n">
-        <v>1.438</v>
+        <v>1.6856</v>
       </c>
       <c r="G43" t="n">
         <v>-1</v>
       </c>
       <c r="H43" t="n">
-        <v>1.438</v>
+        <v>1.6856</v>
       </c>
       <c r="I43" t="n">
-        <v>1.438</v>
+        <v>1.6856</v>
       </c>
       <c r="J43" t="n">
         <v>-1</v>
@@ -2415,7 +2415,7 @@
         <v>65</v>
       </c>
       <c r="M43" t="n">
-        <v>0.4379999999999999</v>
+        <v>0.6856</v>
       </c>
       <c r="N43" t="n">
         <v>170</v>
@@ -2424,415 +2424,415 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>RUBINO</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4228</v>
+        <v>0.583</v>
       </c>
       <c r="C44" t="n">
-        <v>0.2794</v>
+        <v>0.3852</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2506</v>
+        <v>-0.2116</v>
       </c>
       <c r="E44" t="n">
-        <v>0.4228</v>
+        <v>0.583</v>
       </c>
       <c r="F44" t="n">
-        <v>1.1463</v>
+        <v>0.583</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.7235</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1.1463</v>
+        <v>0.583</v>
       </c>
       <c r="I44" t="n">
-        <v>1.1463</v>
+        <v>0.583</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.7235</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="L44" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.4228000000000001</v>
+        <v>0.583</v>
       </c>
       <c r="N44" t="n">
-        <v>225</v>
+        <v>102</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4132</v>
+        <v>0.5396</v>
       </c>
       <c r="C45" t="n">
-        <v>0.273</v>
+        <v>0.3565</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2544</v>
+        <v>-0.2289</v>
       </c>
       <c r="E45" t="n">
-        <v>0.4132</v>
+        <v>0.5396</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4132</v>
+        <v>0.3481</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>0.1915</v>
       </c>
       <c r="H45" t="n">
-        <v>0.4132</v>
+        <v>0.3481</v>
       </c>
       <c r="I45" t="n">
-        <v>0.4132</v>
+        <v>0.3481</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>0.1915</v>
       </c>
       <c r="K45" t="n">
-        <v>102</v>
+        <v>148</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M45" t="n">
-        <v>0.4132</v>
+        <v>0.5396000000000001</v>
       </c>
       <c r="N45" t="n">
-        <v>102</v>
+        <v>225</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ANGE1</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4058</v>
+        <v>0.4991</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2681</v>
+        <v>0.3298</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2574</v>
+        <v>-0.2451</v>
       </c>
       <c r="E46" t="n">
-        <v>0.4058</v>
+        <v>0.4991</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4058</v>
+        <v>1.2174</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>-0.7183</v>
       </c>
       <c r="H46" t="n">
-        <v>0.4058</v>
+        <v>1.2174</v>
       </c>
       <c r="I46" t="n">
-        <v>0.4058</v>
+        <v>1.2174</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>-0.7183</v>
       </c>
       <c r="K46" t="n">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M46" t="n">
-        <v>0.4058</v>
+        <v>0.4991</v>
       </c>
       <c r="N46" t="n">
-        <v>80</v>
+        <v>221</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>ANGE1</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4031</v>
+        <v>0.4058</v>
       </c>
       <c r="C47" t="n">
-        <v>0.2663</v>
+        <v>0.2681</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.2585</v>
+        <v>-0.2822</v>
       </c>
       <c r="E47" t="n">
-        <v>0.4031</v>
+        <v>0.4058</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.1874</v>
+        <v>0.4058</v>
       </c>
       <c r="G47" t="n">
-        <v>0.5905</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.1874</v>
+        <v>0.4058</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.1874</v>
+        <v>0.4058</v>
       </c>
       <c r="J47" t="n">
-        <v>0.5905</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="L47" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.4031</v>
+        <v>0.4058</v>
       </c>
       <c r="N47" t="n">
-        <v>170</v>
+        <v>80</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>markeloff</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.2635</v>
+        <v>0.4032</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1741</v>
+        <v>0.2664</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3149</v>
+        <v>-0.2833</v>
       </c>
       <c r="E48" t="n">
-        <v>0.2635</v>
+        <v>0.4032</v>
       </c>
       <c r="F48" t="n">
-        <v>0.2635</v>
+        <v>-0.1873</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>0.5905</v>
       </c>
       <c r="H48" t="n">
-        <v>0.2635</v>
+        <v>-0.1873</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2635</v>
+        <v>-0.1873</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>0.5905</v>
       </c>
       <c r="K48" t="n">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="M48" t="n">
-        <v>0.2635</v>
+        <v>0.4032</v>
       </c>
       <c r="N48" t="n">
-        <v>84</v>
+        <v>170</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.2158</v>
+        <v>0.3761</v>
       </c>
       <c r="C49" t="n">
-        <v>0.1426</v>
+        <v>0.2485</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3342</v>
+        <v>-0.2941</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2158</v>
+        <v>0.3761</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9341</v>
+        <v>0.3761</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.7183</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.9341</v>
+        <v>0.3761</v>
       </c>
       <c r="I49" t="n">
-        <v>0.9341</v>
+        <v>0.3761</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.7183</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="L49" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.2158</v>
+        <v>0.3761</v>
       </c>
       <c r="N49" t="n">
-        <v>221</v>
+        <v>155</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.1724</v>
+        <v>0.2772</v>
       </c>
       <c r="C50" t="n">
-        <v>0.1139</v>
+        <v>0.1832</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3517</v>
+        <v>-0.3335</v>
       </c>
       <c r="E50" t="n">
-        <v>0.1724</v>
+        <v>0.2772</v>
       </c>
       <c r="F50" t="n">
-        <v>0.484</v>
+        <v>0.8512</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.3116</v>
+        <v>-0.574</v>
       </c>
       <c r="H50" t="n">
-        <v>0.484</v>
+        <v>0.8512</v>
       </c>
       <c r="I50" t="n">
-        <v>0.484</v>
+        <v>0.8512</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.3116</v>
+        <v>-0.574</v>
       </c>
       <c r="K50" t="n">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="L50" t="n">
-        <v>231</v>
+        <v>65</v>
       </c>
       <c r="M50" t="n">
-        <v>0.1724</v>
+        <v>0.2772</v>
       </c>
       <c r="N50" t="n">
-        <v>316</v>
+        <v>170</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>markeloff</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.1344</v>
+        <v>0.2635</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0888</v>
+        <v>0.1741</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3671</v>
+        <v>-0.3389</v>
       </c>
       <c r="E51" t="n">
-        <v>0.1344</v>
+        <v>0.2635</v>
       </c>
       <c r="F51" t="n">
-        <v>0.7084</v>
+        <v>0.2635</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.574</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.7084</v>
+        <v>0.2635</v>
       </c>
       <c r="I51" t="n">
-        <v>0.7084</v>
+        <v>0.2635</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.574</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="L51" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.1344000000000001</v>
+        <v>0.2635</v>
       </c>
       <c r="N51" t="n">
-        <v>170</v>
+        <v>84</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.1041</v>
+        <v>0.1724</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0688</v>
+        <v>0.1139</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.3793</v>
+        <v>-0.3752</v>
       </c>
       <c r="E52" t="n">
-        <v>0.1041</v>
+        <v>0.1724</v>
       </c>
       <c r="F52" t="n">
-        <v>0.1041</v>
+        <v>0.484</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>-0.3116</v>
       </c>
       <c r="H52" t="n">
-        <v>0.1041</v>
+        <v>0.484</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1041</v>
+        <v>0.484</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>-0.3116</v>
       </c>
       <c r="K52" t="n">
-        <v>155</v>
+        <v>85</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="M52" t="n">
-        <v>0.1041</v>
+        <v>0.1724</v>
       </c>
       <c r="N52" t="n">
-        <v>155</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53">
@@ -2848,7 +2848,7 @@
         <v>-0.0326</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4413</v>
+        <v>-0.4636</v>
       </c>
       <c r="E53" t="n">
         <v>-0.0493</v>
@@ -2894,7 +2894,7 @@
         <v>-0.0369</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4439</v>
+        <v>-0.4661</v>
       </c>
       <c r="E54" t="n">
         <v>-0.0558</v>
@@ -2934,28 +2934,28 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.0731</v>
+        <v>-0.0641</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.0483</v>
+        <v>-0.0424</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4509</v>
+        <v>-0.4694</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.0731</v>
+        <v>-0.0641</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.0731</v>
+        <v>-0.0641</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.0731</v>
+        <v>-0.0641</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.0731</v>
+        <v>-0.0641</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.0731</v>
+        <v>-0.0641</v>
       </c>
       <c r="N55" t="n">
         <v>155</v>
@@ -2976,124 +2976,124 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>denis</t>
+          <t>znajder</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.199</v>
+        <v>-0.0669</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.1315</v>
+        <v>-0.0442</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5018</v>
+        <v>-0.4706</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.199</v>
+        <v>-0.0669</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.199</v>
+        <v>-0.0669</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.199</v>
+        <v>-0.0669</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.199</v>
+        <v>-0.0669</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>89</v>
+        <v>126</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.199</v>
+        <v>-0.0669</v>
       </c>
       <c r="N56" t="n">
-        <v>89</v>
+        <v>126</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>WorldEdit</t>
+          <t>denis</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.2449</v>
+        <v>-0.1445</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.1618</v>
+        <v>-0.0955</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5203</v>
+        <v>-0.5014999999999999</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.2449</v>
+        <v>-0.1445</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.2449</v>
+        <v>-0.1445</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.2449</v>
+        <v>-0.1445</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.2449</v>
+        <v>-0.1445</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.2449</v>
+        <v>-0.1445</v>
       </c>
       <c r="N57" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>B1ad3</t>
+          <t>WorldEdit</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.246</v>
+        <v>-0.2449</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.1625</v>
+        <v>-0.1618</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5207000000000001</v>
+        <v>-0.5415</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.246</v>
+        <v>-0.2449</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.246</v>
+        <v>-0.2449</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.246</v>
+        <v>-0.2449</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.246</v>
+        <v>-0.2449</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.246</v>
+        <v>-0.2449</v>
       </c>
       <c r="N58" t="n">
         <v>84</v>
@@ -3114,93 +3114,93 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>B1ad3</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.2523</v>
+        <v>-0.246</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.1667</v>
+        <v>-0.1625</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5233</v>
+        <v>-0.5419</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.2523</v>
+        <v>-0.246</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.2523</v>
+        <v>-0.246</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.2523</v>
+        <v>-0.246</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2523</v>
+        <v>-0.246</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.2523</v>
+        <v>-0.246</v>
       </c>
       <c r="N59" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>znajder</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.2735</v>
+        <v>-0.2523</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.1807</v>
+        <v>-0.1667</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5319</v>
+        <v>-0.5444</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.2735</v>
+        <v>-0.2523</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.2735</v>
+        <v>-0.2523</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.2735</v>
+        <v>-0.2523</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2735</v>
+        <v>-0.2523</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.2735</v>
+        <v>-0.2523</v>
       </c>
       <c r="N60" t="n">
-        <v>126</v>
+        <v>80</v>
       </c>
     </row>
     <row r="61">
@@ -3216,7 +3216,7 @@
         <v>-0.2165</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.5537</v>
+        <v>-0.5745</v>
       </c>
       <c r="E61" t="n">
         <v>-0.3277</v>
@@ -3256,28 +3256,28 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.3454</v>
+        <v>-0.3452</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.2282</v>
+        <v>-0.2281</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.5609</v>
+        <v>-0.5814</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.3454</v>
+        <v>-0.3452</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.3454</v>
+        <v>-0.3452</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.3454</v>
+        <v>-0.3452</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.3454</v>
+        <v>-0.3452</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -3289,7 +3289,7 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.3454</v>
+        <v>-0.3452</v>
       </c>
       <c r="N62" t="n">
         <v>89</v>
@@ -3298,139 +3298,139 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.4813</v>
+        <v>-0.4442</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.318</v>
+        <v>-0.2935</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6158</v>
+        <v>-0.6209</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.4813</v>
+        <v>-0.4442</v>
       </c>
       <c r="F63" t="n">
-        <v>-1.4225</v>
+        <v>-0.4442</v>
       </c>
       <c r="G63" t="n">
-        <v>0.9412</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-1.4225</v>
+        <v>-0.4442</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.4225</v>
+        <v>-0.4442</v>
       </c>
       <c r="J63" t="n">
-        <v>0.9412</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="L63" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.4813000000000001</v>
+        <v>-0.4442</v>
       </c>
       <c r="N63" t="n">
-        <v>243</v>
+        <v>110</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.5412</v>
+        <v>-0.4585</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.3576</v>
+        <v>-0.3029</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.64</v>
+        <v>-0.6266</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.5412</v>
+        <v>-0.4585</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.5412</v>
+        <v>-1.3997</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>0.9412</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.5412</v>
+        <v>-1.3997</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.5412</v>
+        <v>-1.3997</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>0.9412</v>
       </c>
       <c r="K64" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.5412</v>
+        <v>-0.4584999999999999</v>
       </c>
       <c r="N64" t="n">
-        <v>80</v>
+        <v>243</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>Zero</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.6676</v>
+        <v>-0.5412</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.4411</v>
+        <v>-0.3576</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.6911</v>
+        <v>-0.6595</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.6676</v>
+        <v>-0.5412</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.6676</v>
+        <v>-0.5412</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.6676</v>
+        <v>-0.5412</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.6676</v>
+        <v>-0.5412</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.6676</v>
+        <v>-0.5412</v>
       </c>
       <c r="N65" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
     </row>
     <row r="66">
@@ -3440,28 +3440,28 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.7378</v>
+        <v>-0.5844</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.4875</v>
+        <v>-0.3861</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7194</v>
+        <v>-0.6767</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.7378</v>
+        <v>-0.5844</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.7378</v>
+        <v>-0.5844</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.7378</v>
+        <v>-0.5844</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.7378</v>
+        <v>-0.5844</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.7378</v>
+        <v>-0.5844</v>
       </c>
       <c r="N66" t="n">
         <v>141</v>
@@ -3486,28 +3486,28 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.7822</v>
+        <v>-0.6832</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.5168</v>
+        <v>-0.4514</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7374000000000001</v>
+        <v>-0.7161</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.7822</v>
+        <v>-0.6832</v>
       </c>
       <c r="F67" t="n">
-        <v>0.0039</v>
+        <v>0.1029</v>
       </c>
       <c r="G67" t="n">
         <v>-0.7861</v>
       </c>
       <c r="H67" t="n">
-        <v>0.0039</v>
+        <v>0.1029</v>
       </c>
       <c r="I67" t="n">
-        <v>0.0039</v>
+        <v>0.1029</v>
       </c>
       <c r="J67" t="n">
         <v>-0.7861</v>
@@ -3519,7 +3519,7 @@
         <v>77</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.7822</v>
+        <v>-0.6832</v>
       </c>
       <c r="N67" t="n">
         <v>225</v>
@@ -3528,93 +3528,93 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>wayLander</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.9736</v>
+        <v>-0.7528</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.6433</v>
+        <v>-0.4974</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8147</v>
+        <v>-0.7438</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.9736</v>
+        <v>-0.7528</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.9736</v>
+        <v>-0.312</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>-0.4408</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.9736</v>
+        <v>-0.312</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.9736</v>
+        <v>-0.312</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>-0.4408</v>
       </c>
       <c r="K68" t="n">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.9736</v>
+        <v>-0.7528</v>
       </c>
       <c r="N68" t="n">
-        <v>84</v>
+        <v>230</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>wayLander</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.0648</v>
+        <v>-0.9736</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.7035</v>
+        <v>-0.6433</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8515</v>
+        <v>-0.8318</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.0648</v>
+        <v>-0.9736</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.624</v>
+        <v>-0.9736</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.4408</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.624</v>
+        <v>-0.9736</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.624</v>
+        <v>-0.9736</v>
       </c>
       <c r="J69" t="n">
-        <v>-0.4408</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="L69" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-1.0648</v>
+        <v>-0.9736</v>
       </c>
       <c r="N69" t="n">
-        <v>230</v>
+        <v>84</v>
       </c>
     </row>
     <row r="70">
@@ -3630,7 +3630,7 @@
         <v>-0.7365</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8717</v>
+        <v>-0.888</v>
       </c>
       <c r="E70" t="n">
         <v>-1.1147</v>
@@ -3676,7 +3676,7 @@
         <v>-0.7549</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8829</v>
+        <v>-0.8991</v>
       </c>
       <c r="E71" t="n">
         <v>-1.1426</v>
@@ -3722,7 +3722,7 @@
         <v>-0.7964</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9083</v>
+        <v>-0.9241</v>
       </c>
       <c r="E72" t="n">
         <v>-1.2053</v>
@@ -3758,93 +3758,93 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SIXER</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.2713</v>
+        <v>-1.2269</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.84</v>
+        <v>-0.8106</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9349</v>
+        <v>-0.9327</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.2713</v>
+        <v>-1.2269</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.2713</v>
+        <v>-1.2269</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.2713</v>
+        <v>-1.2269</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.2713</v>
+        <v>-1.2269</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.2713</v>
+        <v>-1.2269</v>
       </c>
       <c r="N73" t="n">
-        <v>141</v>
+        <v>155</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>SIXER</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.3465</v>
+        <v>-1.2713</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.8897</v>
+        <v>-0.84</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9653</v>
+        <v>-0.9504</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.3465</v>
+        <v>-1.2713</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.3465</v>
+        <v>-1.2713</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.3465</v>
+        <v>-1.2713</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.3465</v>
+        <v>-1.2713</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.3465</v>
+        <v>-1.2713</v>
       </c>
       <c r="N74" t="n">
-        <v>155</v>
+        <v>141</v>
       </c>
     </row>
     <row r="75">
@@ -3860,7 +3860,7 @@
         <v>-0.8901</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.9656</v>
+        <v>-0.9806</v>
       </c>
       <c r="E75" t="n">
         <v>-1.3471</v>
@@ -3906,7 +3906,7 @@
         <v>-1.126</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1098</v>
+        <v>-1.1229</v>
       </c>
       <c r="E76" t="n">
         <v>-1.7042</v>
@@ -3952,7 +3952,7 @@
         <v>-1.2609</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1923</v>
+        <v>-1.2042</v>
       </c>
       <c r="E77" t="n">
         <v>-1.9084</v>
@@ -3998,7 +3998,7 @@
         <v>-1.4577</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.3126</v>
+        <v>-1.3229</v>
       </c>
       <c r="E78" t="n">
         <v>-2.2062</v>
@@ -4044,7 +4044,7 @@
         <v>-1.4646</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.3169</v>
+        <v>-1.327</v>
       </c>
       <c r="E79" t="n">
         <v>-2.2167</v>
@@ -4090,7 +4090,7 @@
         <v>-1.7314</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.48</v>
+        <v>-1.4879</v>
       </c>
       <c r="E80" t="n">
         <v>-2.6205</v>
@@ -4136,7 +4136,7 @@
         <v>-2.6771</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.0582</v>
+        <v>-2.0581</v>
       </c>
       <c r="E81" t="n">
         <v>-4.0518</v>
